--- a/data/信用债发行汇总_2026-07-28.xlsx
+++ b/data/信用债发行汇总_2026-07-28.xlsx
@@ -37,7 +37,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -92,6 +98,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -711,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:AN18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -961,162 +970,164 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07-27 19:00</t>
+          <t>08-03 18:00</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>26鸿飞02</t>
+          <t>26农业银行绿色债01</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>283448.SH</t>
+          <t>2628001.IB</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>2.34</v>
-      </c>
+          <t>1.20 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>江油鸿飞投资(集团)有限公司</t>
+          <t>中国农业银行股份有限公司</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>四川省-绵阳市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>26鸿飞01</t>
+          <t>25农业银行绿色债02</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>4.67Y</t>
+          <t>3.57Y</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2.2945</t>
+          <t>1.5338</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>四川省金玉融资担保有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,华泰证券股份有限公司,招商证券股份有限公司,中银国际证券股份有限公司,国投证券股份有限公司,中国银河证券股份有限公司,申万宏源证券有限公司,国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>江油鸿飞投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>中国农业银行股份有限公司2026年绿色金融债券(第一期)(债券通)</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2031-07-28</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr"/>
+          <t>2029-08-05</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AG2" s="2" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>国有银行</t>
         </is>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr"/>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AK2" s="2" t="inlineStr">
@@ -1131,7 +1142,7 @@
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AN2" s="2" t="inlineStr"/>
@@ -1139,85 +1150,89 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07-23 19:00</t>
+          <t>07-29 16:30</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>26长开G1</t>
+          <t>26湖南银行债01</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>245671.SH</t>
+          <t>212680010.IB</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>重庆长寿开发投资(集团)有限公司</t>
+          <t>湖南银行股份有限公司</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>重庆市-长寿区</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>24长寿开投MTN003A</t>
+          <t>25湖南银行债01</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>1.10Y+2.00Y</t>
+          <t>2.02Y</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1.7196</t>
+          <t>1.5812</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,东方证券股份有限公司,中国银行股份有限公司,兴业银行股份有限公司,华夏银行股份有限公司,恒丰银行股份有限公司</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
@@ -1227,12 +1242,12 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>湖南银行股份有限公司2026年第一期金融债券</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
@@ -1242,49 +1257,49 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2027-07-28</t>
+          <t>2029-07-31</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AE3" s="2" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AG3" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AI3" s="2" t="inlineStr"/>
@@ -1305,7 +1320,7 @@
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AN3" s="2" t="inlineStr"/>
@@ -1313,89 +1328,89 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>07-23 18:00</t>
+          <t>07-27 19:00</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>26恒丰银行绿债01B</t>
+          <t>26鸿飞02</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>222680007.IB</t>
+          <t>283448.SH</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.85</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>1.6</v>
+        <v>2.34</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>恒丰银行股份有限公司</t>
+          <t>江油鸿飞投资(集团)有限公司</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>四川省-绵阳市</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25恒丰银行债02</t>
+          <t>26鸿飞01</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1.83Y</t>
+          <t>4.67Y</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1.5832</t>
+          <t>2.2945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,德邦证券股份有限公司,中国进出口银行,中国银行股份有限公司,中国建设银行股份有限公司,兴业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr"/>
+          <t>长城证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>四川省金玉融资担保有限公司</t>
+        </is>
+      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -1405,70 +1420,70 @@
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种二)</t>
+          <t>江油鸿飞投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2029-07-27</t>
+          <t>2031-07-28</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AE4" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AF4" s="2" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AG4" s="2" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr"/>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AK4" s="2" t="inlineStr">
@@ -1483,7 +1498,7 @@
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AN4" s="2" t="inlineStr"/>
@@ -1496,84 +1511,80 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>07-23 18:00</t>
+          <t>07-23 19:00</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26恒丰银行绿债01A</t>
+          <t>26长开G1</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>222680006.IB</t>
+          <t>245671.SH</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>恒丰银行股份有限公司</t>
+          <t>重庆长寿开发投资(集团)有限公司</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>重庆市-长寿区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25恒丰银行债02</t>
+          <t>24长寿开投MTN003A</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1.83Y</t>
+          <t>1.10Y+2.00Y</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1.5832</t>
+          <t>1.7196</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,德邦证券股份有限公司,中国进出口银行,中国银行股份有限公司,中国建设银行股份有限公司,兴业银行股份有限公司</t>
+          <t>国投证券股份有限公司</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1583,12 +1594,12 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种一)</t>
+          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1598,14 +1609,14 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2029-07-27</t>
+          <t>2027-07-28</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr"/>
       <c r="Z5" s="2" t="inlineStr"/>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1615,32 +1626,32 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AG5" s="2" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr"/>
@@ -1679,75 +1690,79 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26成都开投PPN001</t>
+          <t>26恒丰银行绿债01B</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>032601649.IB</t>
+          <t>222680007.IB</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.35 ~ 1.85</t>
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>成都经开国投集团有限公司</t>
+          <t>恒丰银行股份有限公司</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25成都开投PPN002</t>
+          <t>25恒丰银行债02</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4.31Y+5.00Y</t>
+          <t>1.83Y</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2.1942</t>
+          <t>1.5832</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,成都银行股份有限公司,国投证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,德邦证券股份有限公司,中国进出口银行,中国银行股份有限公司,中国建设银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr"/>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1762,70 +1777,62 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>成都经开国投集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种二)</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2036-07-24</t>
+          <t>2029-07-27</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr"/>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AG6" s="2" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AH6" s="2" t="inlineStr">
         <is>
-          <t>房屋建设</t>
-        </is>
-      </c>
-      <c r="AI6" s="2" t="inlineStr">
-        <is>
-          <t>2031-07-24</t>
-        </is>
-      </c>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AI6" s="2" t="inlineStr"/>
       <c r="AJ6" s="2" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -1833,7 +1840,7 @@
       </c>
       <c r="AK6" s="2" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AL6" s="2" t="inlineStr">
@@ -1846,75 +1853,73 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="AN6" s="2" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AN6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>07-17 18:00</t>
+          <t>07-23 18:00</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26云能MTN004</t>
+          <t>26恒丰银行绿债01A</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>102682656.IB</t>
+          <t>222680006.IB</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.40</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.14</v>
+        <v>1.56</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司</t>
+          <t>恒丰银行股份有限公司</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>云南省</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24云能投GN001</t>
+          <t>25恒丰银行债02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4.93Y</t>
+          <t>1.83Y</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2.2567</t>
+          <t>1.5832</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1922,16 +1927,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,广发证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,德邦证券股份有限公司,中国进出口银行,中国银行股份有限公司,中国建设银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1946,7 +1955,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司2026年度第四期中期票据</t>
+          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种一)</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1956,57 +1965,49 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2031-07-20</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
+          <t>2029-07-27</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AF7" s="2" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AG7" s="2" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AI7" s="2" t="inlineStr"/>
@@ -2027,7 +2028,7 @@
       </c>
       <c r="AM7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AN7" s="2" t="inlineStr"/>
@@ -2035,31 +2036,31 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>07-15 19:00</t>
+          <t>07-23 18:00</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>26成经02</t>
+          <t>26成都开投PPN001</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>283309.SH</t>
+          <t>032601649.IB</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1.63</v>
+        <v>13</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -2067,11 +2068,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>成都经开产业投资集团有限公司</t>
+          <t>成都经开国投集团有限公司</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2081,22 +2082,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>26成经01</t>
+          <t>25成都开投PPN002</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>4.31Y+5.00Y</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2.3359</t>
+          <t>2.1942</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -2107,13 +2108,13 @@
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,华创证券有限责任公司</t>
+          <t>广发证券股份有限公司,成都银行股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr"/>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -2123,12 +2124,12 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>成都经开产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>成都经开国投集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2138,24 +2139,28 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2031-07-16</t>
+          <t>2036-07-24</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr"/>
-      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -2180,10 +2185,14 @@
       </c>
       <c r="AH8" s="2" t="inlineStr">
         <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI8" s="2" t="inlineStr"/>
+          <t>房屋建设</t>
+        </is>
+      </c>
+      <c r="AI8" s="2" t="inlineStr">
+        <is>
+          <t>2031-07-24</t>
+        </is>
+      </c>
       <c r="AJ8" s="2" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -2191,7 +2200,7 @@
       </c>
       <c r="AK8" s="2" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AL8" s="2" t="inlineStr">
@@ -2201,10 +2210,12 @@
       </c>
       <c r="AM8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="AN8" s="2" t="inlineStr"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AN8" s="2" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2214,80 +2225,80 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>07-15 19:00</t>
+          <t>07-17 18:00</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26长开03</t>
+          <t>26云能MTN004</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>283348.SH</t>
+          <t>102682656.IB</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.80 ~ 2.40</t>
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1.76</v>
+        <v>2.14</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>重庆长寿开发投资(集团)有限公司</t>
+          <t>云南省能源集团有限公司</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>重庆市-长寿区</t>
+          <t>云南省</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26长开02</t>
+          <t>24云能投GN001</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>337D</t>
+          <t>4.93Y</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1.7167</t>
+          <t>2.2567</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>华源证券股份有限公司</t>
+          <t>中国银行股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr"/>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -2297,22 +2308,22 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>云南省能源集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2027-07-18</t>
+          <t>2031-07-20</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -2320,45 +2331,49 @@
           <t>休1</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" s="2" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AF9" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AG9" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr"/>
@@ -2379,7 +2394,7 @@
       </c>
       <c r="AM9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AN9" s="2" t="inlineStr"/>
@@ -2392,80 +2407,80 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07-15 18:00</t>
+          <t>07-15 19:00</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>26华发集团MTN006</t>
+          <t>26成经02</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>102682614.IB</t>
+          <t>283309.SH</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>10</v>
+        <v>1.63</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2.20 ~ 2.79</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>2.79</v>
+        <v>2.29</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司</t>
+          <t>成都经开产业投资集团有限公司</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26华发集团MTN005</t>
+          <t>26成经01</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2.99Y+2.00Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2.7332</t>
+          <t>2.3359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,东莞银行股份有限公司</t>
+          <t>国金证券股份有限公司,华创证券有限责任公司</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr"/>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -2475,33 +2490,29 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司2026年度第六期中期票据</t>
+          <t>成都经开产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2029-07-16</t>
+          <t>2031-07-16</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr"/>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
+      <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -2511,32 +2522,32 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AF10" s="2" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr"/>
@@ -2560,86 +2571,84 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="AN10" s="2" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AN10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07-10 19:00</t>
+          <t>07-15 19:00</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26云能03</t>
+          <t>26长开03</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>245651.SH</t>
+          <t>283348.SH</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.40</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司</t>
+          <t>重庆长寿开发投资(集团)有限公司</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>云南省</t>
+          <t>重庆市-长寿区</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24云能投GN001</t>
+          <t>26长开02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4.95Y</t>
+          <t>337D</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2.2717</t>
+          <t>1.7167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,招商证券股份有限公司,申万宏源证券有限公司</t>
+          <t>华源证券股份有限公司</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr"/>
@@ -2660,17 +2669,17 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2031-07-13</t>
+          <t>2027-07-18</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -2678,49 +2687,45 @@
           <t>休1</t>
         </is>
       </c>
-      <c r="Z11" s="2" t="inlineStr">
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AE11" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AF11" s="2" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AG11" s="2" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr"/>
@@ -2741,7 +2746,7 @@
       </c>
       <c r="AM11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AN11" s="2" t="inlineStr"/>
@@ -2749,63 +2754,63 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>07-10 18:00</t>
+          <t>07-15 18:00</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>26华发集团MTN006</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>102682614.IB</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2.20 ~ 2.79</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>珠海华发集团有限公司</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>广东省-珠海市</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>26华发集团MTN005</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>102682543.IB</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3+2</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2.20 ~ 2.78</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>珠海华发集团有限公司</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>广东省-珠海市</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>24华发集团MTN013</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3.09Y</t>
+          <t>2.99Y+2.00Y</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2.7518</t>
+          <t>2.7332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2821,7 +2826,7 @@
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>上海银行股份有限公司,厦门国际银行股份有限公司</t>
+          <t>江苏银行股份有限公司,东莞银行股份有限公司</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr"/>
@@ -2842,7 +2847,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司2026年度第五期中期票据</t>
+          <t>珠海华发集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -2852,27 +2857,23 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2031-07-13</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-07-16</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2905,11 +2906,7 @@
           <t>综合</t>
         </is>
       </c>
-      <c r="AI12" s="2" t="inlineStr">
-        <is>
-          <t>2029-07-13</t>
-        </is>
-      </c>
+      <c r="AI12" s="2" t="inlineStr"/>
       <c r="AJ12" s="2" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -2917,7 +2914,7 @@
       </c>
       <c r="AK12" s="2" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AL12" s="2" t="inlineStr">
@@ -2927,11 +2924,11 @@
       </c>
       <c r="AM12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AN12" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="13">
@@ -2942,58 +2939,58 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>07-10 18:00</t>
+          <t>07-10 19:00</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26武汉开投PPN003</t>
+          <t>26云能03</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>032680249.IB</t>
+          <t>245651.SH</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.80 ~ 2.40</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>武汉开发投资有限公司</t>
+          <t>云南省能源集团有限公司</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>云南省</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26武开03</t>
+          <t>24云能投GN001</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2.80Y</t>
+          <t>4.95Y</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2.0656</t>
+          <t>2.2717</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3003,23 +3000,19 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,兴业银行股份有限公司,渤海银行股份有限公司,广发银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>武汉金融控股(集团)有限公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司,招商证券股份有限公司,申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr"/>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -3029,28 +3022,32 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>武汉开发投资有限公司2026年度第三期定向债务融资工具</t>
+          <t>云南省能源集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2029-07-13</t>
-        </is>
-      </c>
-      <c r="Y13" s="2" t="inlineStr"/>
+          <t>2031-07-13</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -3070,7 +3067,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" s="2" t="inlineStr">
@@ -3080,23 +3077,23 @@
       </c>
       <c r="AF13" s="2" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AG13" s="2" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AH13" s="2" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AI13" s="2" t="inlineStr"/>
       <c r="AJ13" s="2" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AK13" s="2" t="inlineStr">
@@ -3124,58 +3121,58 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>07-09 18:00</t>
+          <t>07-10 18:00</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>26湖北港口MTN003</t>
+          <t>26华发集团MTN005</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>102682535.IB</t>
+          <t>102682543.IB</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>2.20 ~ 2.78</t>
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1.85</v>
+        <v>2.78</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>湖北港口集团有限公司</t>
+          <t>珠海华发集团有限公司</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>湖北省</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>26湖北港口MTN002</t>
+          <t>24华发集团MTN013</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2.67Y+N</t>
+          <t>3.09Y</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1.8352</t>
+          <t>2.7518</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3191,7 +3188,7 @@
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信银行股份有限公司</t>
+          <t>上海银行股份有限公司,厦门国际银行股份有限公司</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr"/>
@@ -3212,7 +3209,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>湖北港口集团有限公司2026年度第三期中期票据</t>
+          <t>珠海华发集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3222,77 +3219,87 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2029-07-10</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="inlineStr"/>
+          <t>2031-07-13</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr">
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AI14" s="2" t="inlineStr">
+        <is>
+          <t>2029-07-13</t>
+        </is>
+      </c>
+      <c r="AJ14" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AL14" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM14" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="AC14" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AE14" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF14" s="2" t="inlineStr">
-        <is>
-          <t>港口</t>
-        </is>
-      </c>
-      <c r="AG14" s="2" t="inlineStr">
-        <is>
-          <t>港口</t>
-        </is>
-      </c>
-      <c r="AH14" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI14" s="2" t="inlineStr"/>
-      <c r="AJ14" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK14" s="2" t="inlineStr">
-        <is>
-          <t>永续</t>
-        </is>
-      </c>
-      <c r="AL14" s="2" t="inlineStr">
-        <is>
-          <t>次级债权</t>
-        </is>
-      </c>
-      <c r="AM14" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AN14" s="2" t="inlineStr"/>
+      <c r="AN14" s="2" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3302,77 +3309,81 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>07-07 18:00</t>
+          <t>07-10 18:00</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26新都香城PPN003</t>
+          <t>26武汉开投PPN003</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>032680385.IB</t>
+          <t>032680249.IB</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>成都市新都香城建设投资有限公司</t>
+          <t>武汉开发投资有限公司</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26新都香城PPN002</t>
+          <t>26武开03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4.95Y</t>
+          <t>2.80Y</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2.1854</t>
+          <t>2.0656</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司,成都农村商业银行股份有限公司,兴业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr"/>
+          <t>国泰海通证券股份有限公司,兴业银行股份有限公司,渤海银行股份有限公司,广发银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>武汉金融控股(集团)有限公司</t>
+        </is>
+      </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
           <t>定向工具(PPN)</t>
@@ -3390,7 +3401,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>成都市新都香城建设投资有限公司2026年度第三期定向债务融资工具</t>
+          <t>武汉开发投资有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -3400,28 +3411,28 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2031-07-08</t>
+          <t>2029-07-13</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr"/>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
@@ -3431,17 +3442,17 @@
       </c>
       <c r="AE15" s="2" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AF15" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AG15" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AH15" s="2" t="inlineStr">
@@ -3452,7 +3463,7 @@
       <c r="AI15" s="2" t="inlineStr"/>
       <c r="AJ15" s="2" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AK15" s="2" t="inlineStr">
@@ -3467,7 +3478,7 @@
       </c>
       <c r="AM15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AN15" s="2" t="inlineStr"/>
@@ -3480,58 +3491,58 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07-07 18:00</t>
+          <t>07-09 18:00</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>26金融街MTN003</t>
+          <t>26湖北港口MTN003</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>102602112.IB</t>
+          <t>102682535.IB</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>11.4</v>
+        <v>8</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2.10 ~ 2.90</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司</t>
+          <t>湖北港口集团有限公司</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>湖北省</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24金街04</t>
+          <t>26湖北港口MTN002</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2.97Y+2.00Y</t>
+          <t>2.67Y+N</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2.8101</t>
+          <t>1.8352</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3544,14 +3555,10 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,南京银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr"/>
@@ -3572,7 +3579,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司2026年度第三期中期票据</t>
+          <t>湖北港口集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -3582,81 +3589,441 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2031-07-08</t>
+          <t>2029-07-10</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr"/>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AL16" s="2" t="inlineStr">
+        <is>
+          <t>次级债权</t>
+        </is>
+      </c>
+      <c r="AM16" s="2" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
+      <c r="AN16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>07-07 18:00</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>26新都香城PPN003</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>032680385.IB</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>成都市新都香城建设投资有限公司</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>四川省-成都市</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>26新都香城PPN002</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>4.95Y</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2.1854</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>长城证券股份有限公司,成都农村商业银行股份有限公司,兴业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>成都市新都香城建设投资有限公司2026年度第三期定向债务融资工具</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>2031-07-08</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
+      <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="AC16" s="2" t="inlineStr">
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH17" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL17" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AN17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>07-07 18:00</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>26金融街MTN003</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>102602112.IB</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2.10 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>金融街控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>24金街04</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2.97Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2.8101</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,南京银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>金融街控股股份有限公司2026年度第三期中期票据</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>2031-07-08</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>产业</t>
         </is>
       </c>
-      <c r="AD16" s="2" t="inlineStr">
+      <c r="AD18" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AE16" s="2" t="inlineStr">
+      <c r="AE18" s="2" t="inlineStr">
         <is>
           <t>房地产</t>
         </is>
       </c>
-      <c r="AF16" s="2" t="inlineStr">
+      <c r="AF18" s="2" t="inlineStr">
         <is>
           <t>房地产开发</t>
         </is>
       </c>
-      <c r="AG16" s="2" t="inlineStr">
+      <c r="AG18" s="2" t="inlineStr">
         <is>
           <t>住宅楼房</t>
         </is>
       </c>
-      <c r="AH16" s="2" t="inlineStr">
+      <c r="AH18" s="2" t="inlineStr">
         <is>
           <t>房地产开发</t>
         </is>
       </c>
-      <c r="AI16" s="2" t="inlineStr">
+      <c r="AI18" s="2" t="inlineStr">
         <is>
           <t>2029-07-08</t>
         </is>
       </c>
-      <c r="AJ16" s="2" t="inlineStr">
+      <c r="AJ18" s="2" t="inlineStr">
         <is>
           <t>无担保</t>
         </is>
       </c>
-      <c r="AK16" s="2" t="inlineStr">
+      <c r="AK18" s="2" t="inlineStr">
         <is>
           <t>含权</t>
         </is>
       </c>
-      <c r="AL16" s="2" t="inlineStr">
+      <c r="AL18" s="2" t="inlineStr">
         <is>
           <t>普通债权</t>
         </is>
       </c>
-      <c r="AM16" s="2" t="inlineStr">
+      <c r="AM18" s="2" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="AN16" s="2" t="inlineStr"/>
+      <c r="AN18" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
